--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -1826,7 +1826,7 @@
         <v>111983906</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>111985289</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4198,6 +4198,114 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111984637</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92957</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mellandammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>396547</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6849665</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>92957</v>
+        <v>93044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>93047</v>
+        <v>93073</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>93073</v>
+        <v>93074</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>93074</v>
+        <v>93075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>93075</v>
+        <v>93077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 30214-2023 artfynd.xlsx
+++ b/artfynd/A 30214-2023 artfynd.xlsx
@@ -4203,7 +4203,7 @@
         <v>111984637</v>
       </c>
       <c r="B33" t="n">
-        <v>93077</v>
+        <v>93081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
